--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/132.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/132.xlsx
@@ -426,13 +426,13 @@
         <v>-18.66896298908703</v>
       </c>
       <c r="E2">
-        <v>-17.94333313389013</v>
+        <v>-16.70044815774492</v>
       </c>
       <c r="F2">
-        <v>-2.668695908230688</v>
+        <v>-1.658269917643906</v>
       </c>
       <c r="G2">
-        <v>-12.85334435982237</v>
+        <v>-8.93001727218836</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.34642948542804</v>
       </c>
       <c r="E3">
-        <v>-18.32099880918182</v>
+        <v>-15.86411146411233</v>
       </c>
       <c r="F3">
-        <v>-2.603638417517023</v>
+        <v>-1.80430529218564</v>
       </c>
       <c r="G3">
-        <v>-12.61129520782525</v>
+        <v>-10.29568793500173</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.998691664718</v>
       </c>
       <c r="E4">
-        <v>-18.71856259926322</v>
+        <v>-15.05948767395545</v>
       </c>
       <c r="F4">
-        <v>-2.70204432313259</v>
+        <v>-1.950503026738322</v>
       </c>
       <c r="G4">
-        <v>-12.19891128223424</v>
+        <v>-9.55602512740702</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.65119061305814</v>
       </c>
       <c r="E5">
-        <v>-19.37255123002895</v>
+        <v>-17.20792706894049</v>
       </c>
       <c r="F5">
-        <v>-2.481756579706117</v>
+        <v>-1.558022551291916</v>
       </c>
       <c r="G5">
-        <v>-12.60756117769061</v>
+        <v>-11.1274743190994</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.30880440114622</v>
       </c>
       <c r="E6">
-        <v>-19.86256834545094</v>
+        <v>-16.8332728288639</v>
       </c>
       <c r="F6">
-        <v>-2.39797384385217</v>
+        <v>-1.16767263680551</v>
       </c>
       <c r="G6">
-        <v>-12.26696381737713</v>
+        <v>-10.49154404988498</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.97574501621619</v>
       </c>
       <c r="E7">
-        <v>-20.14822901432879</v>
+        <v>-16.85783980035551</v>
       </c>
       <c r="F7">
-        <v>-2.604111415304021</v>
+        <v>-0.5935891756433691</v>
       </c>
       <c r="G7">
-        <v>-12.12502801638023</v>
+        <v>-9.291581638266692</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.65960008583458</v>
       </c>
       <c r="E8">
-        <v>-20.78403582195373</v>
+        <v>-17.76492031493593</v>
       </c>
       <c r="F8">
-        <v>-2.349163123009612</v>
+        <v>-1.661308369277375</v>
       </c>
       <c r="G8">
-        <v>-11.68514745412107</v>
+        <v>-8.862972072064226</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.36527799426036</v>
       </c>
       <c r="E9">
-        <v>-21.75058425720287</v>
+        <v>-19.38333352664121</v>
       </c>
       <c r="F9">
-        <v>-2.181311036180348</v>
+        <v>-1.179809047623926</v>
       </c>
       <c r="G9">
-        <v>-11.71288033874149</v>
+        <v>-8.39318317529073</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.08392591727069</v>
       </c>
       <c r="E10">
-        <v>-22.50950668767434</v>
+        <v>-20.38440704772484</v>
       </c>
       <c r="F10">
-        <v>-1.983028044441842</v>
+        <v>-0.8413613211273264</v>
       </c>
       <c r="G10">
-        <v>-11.54526897904194</v>
+        <v>-8.379438138178216</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.81746411795296</v>
       </c>
       <c r="E11">
-        <v>-22.92937774071752</v>
+        <v>-20.94777638512307</v>
       </c>
       <c r="F11">
-        <v>-2.095852513070537</v>
+        <v>-0.7373755326865017</v>
       </c>
       <c r="G11">
-        <v>-11.11243319947091</v>
+        <v>-6.614373905927679</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.56243154543805</v>
       </c>
       <c r="E12">
-        <v>-23.3902812967442</v>
+        <v>-21.00722166342176</v>
       </c>
       <c r="F12">
-        <v>-2.336500698890418</v>
+        <v>-0.1595851273968325</v>
       </c>
       <c r="G12">
-        <v>-10.72026816112919</v>
+        <v>-6.225266966079368</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.30957164672201</v>
       </c>
       <c r="E13">
-        <v>-23.16446441187771</v>
+        <v>-20.91536609665017</v>
       </c>
       <c r="F13">
-        <v>-2.216326126296683</v>
+        <v>-0.1718681592455436</v>
       </c>
       <c r="G13">
-        <v>-10.24220730480434</v>
+        <v>-6.238683881035938</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.06787439440027</v>
       </c>
       <c r="E14">
-        <v>-24.72565582602207</v>
+        <v>-21.92602186873403</v>
       </c>
       <c r="F14">
-        <v>-2.2534071647156</v>
+        <v>0.04328122118136361</v>
       </c>
       <c r="G14">
-        <v>-9.172578294748751</v>
+        <v>-6.316245396258092</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.83182722180665</v>
       </c>
       <c r="E15">
-        <v>-25.53009394874463</v>
+        <v>-22.19509473732179</v>
       </c>
       <c r="F15">
-        <v>-1.832771309615442</v>
+        <v>-0.92713131038059</v>
       </c>
       <c r="G15">
-        <v>-9.062673778615151</v>
+        <v>-5.562689896580697</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.59830562263059</v>
       </c>
       <c r="E16">
-        <v>-26.30163723627548</v>
+        <v>-24.58401421601015</v>
       </c>
       <c r="F16">
-        <v>-2.097799176467116</v>
+        <v>0.1149325164213125</v>
       </c>
       <c r="G16">
-        <v>-8.887863418814174</v>
+        <v>-6.677452109186444</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.36801624132169</v>
       </c>
       <c r="E17">
-        <v>-27.17423342128748</v>
+        <v>-23.99922066808163</v>
       </c>
       <c r="F17">
-        <v>-1.743911509949736</v>
+        <v>0.09025627985931799</v>
       </c>
       <c r="G17">
-        <v>-8.101367735901514</v>
+        <v>-6.302145987217157</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.13594076228389</v>
       </c>
       <c r="E18">
-        <v>-27.39381912591942</v>
+        <v>-24.86837974132181</v>
       </c>
       <c r="F18">
-        <v>-1.817773717787757</v>
+        <v>-0.1825897185399776</v>
       </c>
       <c r="G18">
-        <v>-7.74282865610099</v>
+        <v>-3.899694623379807</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.90062535542152</v>
       </c>
       <c r="E19">
-        <v>-28.31419071171235</v>
+        <v>-25.88533914922435</v>
       </c>
       <c r="F19">
-        <v>-1.671156829329258</v>
+        <v>0.03933653560923237</v>
       </c>
       <c r="G19">
-        <v>-7.39666962524425</v>
+        <v>-4.277067914931544</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.66500661189312</v>
       </c>
       <c r="E20">
-        <v>-28.83802647102363</v>
+        <v>-25.7834711264218</v>
       </c>
       <c r="F20">
-        <v>-1.505431161622981</v>
+        <v>-0.2983316971613329</v>
       </c>
       <c r="G20">
-        <v>-7.451492275059453</v>
+        <v>-3.609946353573041</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.42014871317371</v>
       </c>
       <c r="E21">
-        <v>-29.7030465190208</v>
+        <v>-27.47137830024879</v>
       </c>
       <c r="F21">
-        <v>-1.363111014882803</v>
+        <v>0.4374292002096048</v>
       </c>
       <c r="G21">
-        <v>-6.767492109999167</v>
+        <v>-3.535807152437388</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.16763330151363</v>
       </c>
       <c r="E22">
-        <v>-30.51007719311276</v>
+        <v>-28.42784182388285</v>
       </c>
       <c r="F22">
-        <v>-1.232245532588538</v>
+        <v>-0.3021894041561702</v>
       </c>
       <c r="G22">
-        <v>-6.461478824922233</v>
+        <v>-1.896439955686059</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.90791037687611</v>
       </c>
       <c r="E23">
-        <v>-30.28983712398671</v>
+        <v>-28.09857195031114</v>
       </c>
       <c r="F23">
-        <v>-1.174779200754127</v>
+        <v>0.1491084703586117</v>
       </c>
       <c r="G23">
-        <v>-6.082113831883914</v>
+        <v>-1.370542170246058</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.63854142722348</v>
       </c>
       <c r="E24">
-        <v>-30.88586808016527</v>
+        <v>-30.00057405403576</v>
       </c>
       <c r="F24">
-        <v>-1.145990948404636</v>
+        <v>-0.1461597768996609</v>
       </c>
       <c r="G24">
-        <v>-5.920854917123444</v>
+        <v>-1.002307080737374</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.37019894999465</v>
       </c>
       <c r="E25">
-        <v>-30.83943310769062</v>
+        <v>-28.7837527100417</v>
       </c>
       <c r="F25">
-        <v>-0.6954560002678327</v>
+        <v>0.2954478557371723</v>
       </c>
       <c r="G25">
-        <v>-6.10536456785414</v>
+        <v>-0.03246001830450258</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.10793333345687</v>
       </c>
       <c r="E26">
-        <v>-31.36474062105439</v>
+        <v>-28.2237118010391</v>
       </c>
       <c r="F26">
-        <v>-0.8775460660164144</v>
+        <v>-0.4906297344146129</v>
       </c>
       <c r="G26">
-        <v>-5.976514278436305</v>
+        <v>-0.7890014296009924</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.85389847075808</v>
       </c>
       <c r="E27">
-        <v>-31.81525812194448</v>
+        <v>-29.66086378363935</v>
       </c>
       <c r="F27">
-        <v>-0.9835870339835847</v>
+        <v>-0.4256078634992685</v>
       </c>
       <c r="G27">
-        <v>-6.484342376748445</v>
+        <v>0.8683796735116874</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.61642791795838</v>
       </c>
       <c r="E28">
-        <v>-31.74220025077873</v>
+        <v>-27.24827397131289</v>
       </c>
       <c r="F28">
-        <v>-0.8748903201230392</v>
+        <v>-0.7725579530182023</v>
       </c>
       <c r="G28">
-        <v>-5.826083394822002</v>
+        <v>0.1020963154052063</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.39895427129284</v>
       </c>
       <c r="E29">
-        <v>-31.73611851018643</v>
+        <v>-31.57779626616727</v>
       </c>
       <c r="F29">
-        <v>-0.8509546440191474</v>
+        <v>-0.1311762673178235</v>
       </c>
       <c r="G29">
-        <v>-5.839608590090033</v>
+        <v>-1.339373846652892</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.20227173247654</v>
       </c>
       <c r="E30">
-        <v>-31.71048508306601</v>
+        <v>-29.4252676591533</v>
       </c>
       <c r="F30">
-        <v>-0.7672597151098967</v>
+        <v>-0.4245177319971844</v>
       </c>
       <c r="G30">
-        <v>-5.91396435184861</v>
+        <v>1.056574136053639</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.03459396894221</v>
       </c>
       <c r="E31">
-        <v>-31.24152310754268</v>
+        <v>-29.31915419196856</v>
       </c>
       <c r="F31">
-        <v>-0.9291334743931564</v>
+        <v>-0.2473846167869549</v>
       </c>
       <c r="G31">
-        <v>-6.268175500412227</v>
+        <v>-0.7278033662957889</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.89099235958986</v>
       </c>
       <c r="E32">
-        <v>-30.92649075625108</v>
+        <v>-28.2270175870647</v>
       </c>
       <c r="F32">
-        <v>-0.7968746781273818</v>
+        <v>-0.9447515134055383</v>
       </c>
       <c r="G32">
-        <v>-6.377039869311483</v>
+        <v>-0.7304709994236175</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.76971094376744</v>
       </c>
       <c r="E33">
-        <v>-30.59764429499908</v>
+        <v>-29.36387740126832</v>
       </c>
       <c r="F33">
-        <v>-0.8657285766480767</v>
+        <v>-1.073261947173645</v>
       </c>
       <c r="G33">
-        <v>-6.542721870734085</v>
+        <v>0.3104177909927919</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.66881895563803</v>
       </c>
       <c r="E34">
-        <v>-30.30147077371242</v>
+        <v>-31.10918071890552</v>
       </c>
       <c r="F34">
-        <v>-0.6506877123509363</v>
+        <v>-0.2846346421560431</v>
       </c>
       <c r="G34">
-        <v>-6.247142870216186</v>
+        <v>-0.9403871486890932</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.58222504877317</v>
       </c>
       <c r="E35">
-        <v>-30.32218627806051</v>
+        <v>-28.23063130932282</v>
       </c>
       <c r="F35">
-        <v>-0.8094559222411006</v>
+        <v>-0.8262378174544158</v>
       </c>
       <c r="G35">
-        <v>-6.49447150770245</v>
+        <v>-0.02446040014257636</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.51000924120422</v>
       </c>
       <c r="E36">
-        <v>-29.59806517033799</v>
+        <v>-26.57636164042481</v>
       </c>
       <c r="F36">
-        <v>-0.6964251901291081</v>
+        <v>-1.044228498072925</v>
       </c>
       <c r="G36">
-        <v>-6.885094371911225</v>
+        <v>-1.436468473818421</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.45185821191929</v>
       </c>
       <c r="E37">
-        <v>-29.6993241133865</v>
+        <v>-26.99915355920293</v>
       </c>
       <c r="F37">
-        <v>-0.6195328143316468</v>
+        <v>-0.5479784380778255</v>
       </c>
       <c r="G37">
-        <v>-6.892336027892919</v>
+        <v>-0.8962022191696106</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.40014250477464</v>
       </c>
       <c r="E38">
-        <v>-28.97392597599382</v>
+        <v>-27.67434450527258</v>
       </c>
       <c r="F38">
-        <v>-0.6557730598367224</v>
+        <v>-0.5896883935435863</v>
       </c>
       <c r="G38">
-        <v>-7.168349104251849</v>
+        <v>-0.6547338433885146</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.35686954335245</v>
       </c>
       <c r="E39">
-        <v>-28.58843056914286</v>
+        <v>-25.28878968277191</v>
       </c>
       <c r="F39">
-        <v>-0.6528746022943269</v>
+        <v>0.07017831075026357</v>
       </c>
       <c r="G39">
-        <v>-7.489981003951739</v>
+        <v>-3.508891291985263</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.32174604560271</v>
       </c>
       <c r="E40">
-        <v>-28.33615833912356</v>
+        <v>-24.77435503550056</v>
       </c>
       <c r="F40">
-        <v>-0.817535817888007</v>
+        <v>-0.3298046882632973</v>
       </c>
       <c r="G40">
-        <v>-7.229077952874052</v>
+        <v>-1.766572487584797</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.29164001397538</v>
       </c>
       <c r="E41">
-        <v>-26.73228605745691</v>
+        <v>-26.05612601794963</v>
       </c>
       <c r="F41">
-        <v>-0.532123485988243</v>
+        <v>-0.3776470476119828</v>
       </c>
       <c r="G41">
-        <v>-7.134509866309296</v>
+        <v>-2.304555012028234</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.273994846928</v>
       </c>
       <c r="E42">
-        <v>-26.98363447877865</v>
+        <v>-22.21458981792481</v>
       </c>
       <c r="F42">
-        <v>-0.5134380024832945</v>
+        <v>0.3408854645155308</v>
       </c>
       <c r="G42">
-        <v>-7.48660790818863</v>
+        <v>-1.69517310645128</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.2675888216786</v>
       </c>
       <c r="E43">
-        <v>-26.70090373258375</v>
+        <v>-23.43832387749158</v>
       </c>
       <c r="F43">
-        <v>-0.6227062898517717</v>
+        <v>0.3693755046000142</v>
       </c>
       <c r="G43">
-        <v>-7.329762236425613</v>
+        <v>-2.83149294470258</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.27208422442029</v>
       </c>
       <c r="E44">
-        <v>-25.75521344861394</v>
+        <v>-22.65065469401942</v>
       </c>
       <c r="F44">
-        <v>-0.4618423104325245</v>
+        <v>-0.4583913318324618</v>
       </c>
       <c r="G44">
-        <v>-7.520972141580694</v>
+        <v>-1.759563798333823</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.29154394966838</v>
       </c>
       <c r="E45">
-        <v>-24.99946094994784</v>
+        <v>-22.21711670642109</v>
       </c>
       <c r="F45">
-        <v>-0.5761247056901471</v>
+        <v>0.3872558149894415</v>
       </c>
       <c r="G45">
-        <v>-7.7874401444232</v>
+        <v>-4.194148164902816</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.32658066285245</v>
       </c>
       <c r="E46">
-        <v>-24.18862409345244</v>
+        <v>-22.12378938559701</v>
       </c>
       <c r="F46">
-        <v>-0.3775940320982036</v>
+        <v>-0.0007837828105560845</v>
       </c>
       <c r="G46">
-        <v>-7.681637155238905</v>
+        <v>-2.903768411992468</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.37926585361348</v>
       </c>
       <c r="E47">
-        <v>-23.86782699474907</v>
+        <v>-20.90500947659463</v>
       </c>
       <c r="F47">
-        <v>-0.2259506102395177</v>
+        <v>0.4318468322821389</v>
       </c>
       <c r="G47">
-        <v>-8.624502732788462</v>
+        <v>-4.598345442703013</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.45455199699782</v>
       </c>
       <c r="E48">
-        <v>-23.92530238685443</v>
+        <v>-21.60764750362477</v>
       </c>
       <c r="F48">
-        <v>-0.3517630513767066</v>
+        <v>0.5786492750388645</v>
       </c>
       <c r="G48">
-        <v>-8.288075805077037</v>
+        <v>-2.666040628789139</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.54615577843714</v>
       </c>
       <c r="E49">
-        <v>-22.11521245582648</v>
+        <v>-20.50139564523899</v>
       </c>
       <c r="F49">
-        <v>-0.5125085742573535</v>
+        <v>1.284717342856454</v>
       </c>
       <c r="G49">
-        <v>-8.209221488560461</v>
+        <v>-4.366038237515887</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.65594193072303</v>
       </c>
       <c r="E50">
-        <v>-21.92128508492201</v>
+        <v>-18.47446879330177</v>
       </c>
       <c r="F50">
-        <v>-0.2065775817902457</v>
+        <v>0.5522599746878807</v>
       </c>
       <c r="G50">
-        <v>-7.994222727099406</v>
+        <v>-4.717043632615926</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.78303063487157</v>
       </c>
       <c r="E51">
-        <v>-21.68804150268294</v>
+        <v>-18.90280356426528</v>
       </c>
       <c r="F51">
-        <v>-0.3094674401571667</v>
+        <v>1.047617054622763</v>
       </c>
       <c r="G51">
-        <v>-8.701178318189568</v>
+        <v>-6.018441727522889</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.92234990071336</v>
       </c>
       <c r="E52">
-        <v>-21.01075840162175</v>
+        <v>-17.09418991576385</v>
       </c>
       <c r="F52">
-        <v>-0.1792389723956536</v>
+        <v>1.017881978331872</v>
       </c>
       <c r="G52">
-        <v>-8.326781094592247</v>
+        <v>-4.905146220954213</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.07518916423315</v>
       </c>
       <c r="E53">
-        <v>-20.25595688249727</v>
+        <v>-17.50258581567159</v>
       </c>
       <c r="F53">
-        <v>-0.1668192599254806</v>
+        <v>0.3833227265609495</v>
       </c>
       <c r="G53">
-        <v>-8.819666509922675</v>
+        <v>-4.95309143038082</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.23830577875369</v>
       </c>
       <c r="E54">
-        <v>-19.70762207880449</v>
+        <v>-15.77783497731819</v>
       </c>
       <c r="F54">
-        <v>-0.256924095797594</v>
+        <v>1.185800334553359</v>
       </c>
       <c r="G54">
-        <v>-9.012362808444186</v>
+        <v>-5.357118084659926</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.4031659484045</v>
       </c>
       <c r="E55">
-        <v>-20.03874862671936</v>
+        <v>-15.23164214183105</v>
       </c>
       <c r="F55">
-        <v>-0.4431344610077005</v>
+        <v>1.276272965552316</v>
       </c>
       <c r="G55">
-        <v>-9.403979882785471</v>
+        <v>-5.075868178692121</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.56928650029456</v>
       </c>
       <c r="E56">
-        <v>-19.17549921205918</v>
+        <v>-15.96789955989413</v>
       </c>
       <c r="F56">
-        <v>-0.33602821256053</v>
+        <v>0.4536138425255015</v>
       </c>
       <c r="G56">
-        <v>-9.228562496995997</v>
+        <v>-6.72616512445796</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.7324686283239</v>
       </c>
       <c r="E57">
-        <v>-19.10899404278253</v>
+        <v>-13.57739511530307</v>
       </c>
       <c r="F57">
-        <v>-0.3605462309485898</v>
+        <v>0.1822763011667039</v>
       </c>
       <c r="G57">
-        <v>-9.207579085123349</v>
+        <v>-6.490324043651312</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.886759789651</v>
       </c>
       <c r="E58">
-        <v>-17.84686758057873</v>
+        <v>-16.09670294609429</v>
       </c>
       <c r="F58">
-        <v>-0.2998244152211776</v>
+        <v>0.6184440450693528</v>
       </c>
       <c r="G58">
-        <v>-9.711804402163217</v>
+        <v>-5.962352526185741</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.03385743332735</v>
       </c>
       <c r="E59">
-        <v>-17.71182848567</v>
+        <v>-14.10371700684456</v>
       </c>
       <c r="F59">
-        <v>-0.289167468584162</v>
+        <v>-0.1372316330322879</v>
       </c>
       <c r="G59">
-        <v>-9.706954756698359</v>
+        <v>-6.551046329830396</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.16538875394095</v>
       </c>
       <c r="E60">
-        <v>-17.6918715007182</v>
+        <v>-16.09336546075064</v>
       </c>
       <c r="F60">
-        <v>-0.4882887681343016</v>
+        <v>0.4025681864301904</v>
       </c>
       <c r="G60">
-        <v>-9.753249511680565</v>
+        <v>-6.786598663139813</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.27833784432438</v>
       </c>
       <c r="E61">
-        <v>-17.35728067018747</v>
+        <v>-13.63117980109218</v>
       </c>
       <c r="F61">
-        <v>-0.4954500043315033</v>
+        <v>0.1511578513131376</v>
       </c>
       <c r="G61">
-        <v>-10.28839049825352</v>
+        <v>-6.919954069758766</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.37249744130613</v>
       </c>
       <c r="E62">
-        <v>-16.8068808823472</v>
+        <v>-13.40395003233529</v>
       </c>
       <c r="F62">
-        <v>-0.7599733954348722</v>
+        <v>0.1733986877109016</v>
       </c>
       <c r="G62">
-        <v>-10.08667084044354</v>
+        <v>-6.778641700858159</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.44436499505362</v>
       </c>
       <c r="E63">
-        <v>-17.23092265995144</v>
+        <v>-14.07971609460391</v>
       </c>
       <c r="F63">
-        <v>-0.6219359081671681</v>
+        <v>-0.40840184417572</v>
       </c>
       <c r="G63">
-        <v>-10.39793736123714</v>
+        <v>-7.522425722731528</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.49589790728945</v>
       </c>
       <c r="E64">
-        <v>-16.20558557513472</v>
+        <v>-15.62490388160516</v>
       </c>
       <c r="F64">
-        <v>-0.579723962055311</v>
+        <v>0.1237446888522936</v>
       </c>
       <c r="G64">
-        <v>-10.44741490113201</v>
+        <v>-5.61490069403458</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.53085190010891</v>
       </c>
       <c r="E65">
-        <v>-16.77922096310835</v>
+        <v>-13.45694676364706</v>
       </c>
       <c r="F65">
-        <v>-0.822650986600294</v>
+        <v>0.04141905125987033</v>
       </c>
       <c r="G65">
-        <v>-10.54253423291875</v>
+        <v>-7.124357766804374</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.54365494962995</v>
       </c>
       <c r="E66">
-        <v>-16.6489503513297</v>
+        <v>-14.09564273768889</v>
       </c>
       <c r="F66">
-        <v>-0.7971231883482216</v>
+        <v>-0.0185183005370907</v>
       </c>
       <c r="G66">
-        <v>-10.47765463902385</v>
+        <v>-7.671051934488136</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.53947483705915</v>
       </c>
       <c r="E67">
-        <v>-16.01395866902614</v>
+        <v>-12.78856664248495</v>
       </c>
       <c r="F67">
-        <v>-1.033446467958087</v>
+        <v>0.2269982005090436</v>
       </c>
       <c r="G67">
-        <v>-9.99348086693375</v>
+        <v>-7.997323481473081</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.51936677785575</v>
       </c>
       <c r="E68">
-        <v>-16.06669727731947</v>
+        <v>-13.006445112416</v>
       </c>
       <c r="F68">
-        <v>-0.9860133221063845</v>
+        <v>-0.4786416013612985</v>
       </c>
       <c r="G68">
-        <v>-10.43201284713198</v>
+        <v>-7.981370182251061</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.48048692845237</v>
       </c>
       <c r="E69">
-        <v>-14.97262248554032</v>
+        <v>-13.1382237060392</v>
       </c>
       <c r="F69">
-        <v>-0.972554836913101</v>
+        <v>-0.1648601710178598</v>
       </c>
       <c r="G69">
-        <v>-10.47100360292286</v>
+        <v>-8.667732826834147</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.42989160429754</v>
       </c>
       <c r="E70">
-        <v>-15.44240185062204</v>
+        <v>-12.34268856321572</v>
       </c>
       <c r="F70">
-        <v>-1.142336191423485</v>
+        <v>-0.7521618908264729</v>
       </c>
       <c r="G70">
-        <v>-10.11824603551008</v>
+        <v>-7.46439075700963</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.36622472059098</v>
       </c>
       <c r="E71">
-        <v>-15.88657269519037</v>
+        <v>-14.10056971740923</v>
       </c>
       <c r="F71">
-        <v>-1.33128016906283</v>
+        <v>-0.2331060478648998</v>
       </c>
       <c r="G71">
-        <v>-10.30257850027656</v>
+        <v>-8.252914234846028</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.28755812629318</v>
       </c>
       <c r="E72">
-        <v>-15.83202269729398</v>
+        <v>-12.59808091182631</v>
       </c>
       <c r="F72">
-        <v>-1.091185332668018</v>
+        <v>-0.02277279551786896</v>
       </c>
       <c r="G72">
-        <v>-9.875350328350621</v>
+        <v>-8.182105473593211</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.196999787889</v>
       </c>
       <c r="E73">
-        <v>-15.84698930388933</v>
+        <v>-15.76741043015254</v>
       </c>
       <c r="F73">
-        <v>-1.265920324247143</v>
+        <v>-0.2478948911070794</v>
       </c>
       <c r="G73">
-        <v>-9.615379144195815</v>
+        <v>-7.965226572178593</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.09410407468454</v>
       </c>
       <c r="E74">
-        <v>-16.02245408626453</v>
+        <v>-12.49648459746422</v>
       </c>
       <c r="F74">
-        <v>-1.463065967541606</v>
+        <v>-0.5976779971435875</v>
       </c>
       <c r="G74">
-        <v>-9.837124097183089</v>
+        <v>-8.8749485307562</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.98010867468809</v>
       </c>
       <c r="E75">
-        <v>-16.64088966759604</v>
+        <v>-15.54249471161357</v>
       </c>
       <c r="F75">
-        <v>-1.730097655140652</v>
+        <v>-0.6505062998897231</v>
       </c>
       <c r="G75">
-        <v>-10.01230851624184</v>
+        <v>-5.980274558343428</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.86238939621005</v>
       </c>
       <c r="E76">
-        <v>-16.67558683544281</v>
+        <v>-16.06982645285877</v>
       </c>
       <c r="F76">
-        <v>-1.573262854768621</v>
+        <v>-0.9912494324594802</v>
       </c>
       <c r="G76">
-        <v>-9.158931694283021</v>
+        <v>-6.752254117077105</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.73782289807789</v>
       </c>
       <c r="E77">
-        <v>-16.8391190888078</v>
+        <v>-13.84463848039173</v>
       </c>
       <c r="F77">
-        <v>-1.845649937626766</v>
+        <v>-0.8150846787431233</v>
       </c>
       <c r="G77">
-        <v>-8.831209847368802</v>
+        <v>-7.24391891798742</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.60964202153311</v>
       </c>
       <c r="E78">
-        <v>-17.22299783043802</v>
+        <v>-14.42139851543065</v>
       </c>
       <c r="F78">
-        <v>-1.762701367747437</v>
+        <v>-0.7726962903744697</v>
       </c>
       <c r="G78">
-        <v>-8.847780016243998</v>
+        <v>-7.432825405607772</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.47966975916968</v>
       </c>
       <c r="E79">
-        <v>-18.05698877453464</v>
+        <v>-15.5400900919155</v>
       </c>
       <c r="F79">
-        <v>-1.808925097191053</v>
+        <v>-1.25201534902375</v>
       </c>
       <c r="G79">
-        <v>-9.013488267439074</v>
+        <v>-6.789020204650684</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.34599356540852</v>
       </c>
       <c r="E80">
-        <v>-18.41703868593649</v>
+        <v>-15.67753833499631</v>
       </c>
       <c r="F80">
-        <v>-1.806493838863836</v>
+        <v>-1.482612953145466</v>
       </c>
       <c r="G80">
-        <v>-7.912454685838044</v>
+        <v>-4.959105909499281</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.21448123690367</v>
       </c>
       <c r="E81">
-        <v>-18.52609792546322</v>
+        <v>-16.37995899527407</v>
       </c>
       <c r="F81">
-        <v>-1.905854852094831</v>
+        <v>-1.435071291163996</v>
       </c>
       <c r="G81">
-        <v>-7.945401431516428</v>
+        <v>-7.091742424503494</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.08759512023528</v>
       </c>
       <c r="E82">
-        <v>-19.1513081039102</v>
+        <v>-17.55216807758157</v>
       </c>
       <c r="F82">
-        <v>-1.739423415361368</v>
+        <v>-0.6622997666033796</v>
       </c>
       <c r="G82">
-        <v>-7.192525144701838</v>
+        <v>-6.740395782361272</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.96212384379183</v>
       </c>
       <c r="E83">
-        <v>-20.26623199002067</v>
+        <v>-18.32434535147349</v>
       </c>
       <c r="F83">
-        <v>-1.757380763919256</v>
+        <v>-1.091085928579682</v>
       </c>
       <c r="G83">
-        <v>-7.008789862259172</v>
+        <v>-4.619410885114648</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.84168506292413</v>
       </c>
       <c r="E84">
-        <v>-20.68545999975476</v>
+        <v>-18.13443926548782</v>
       </c>
       <c r="F84">
-        <v>-1.85543047155162</v>
+        <v>-0.2768223091802409</v>
       </c>
       <c r="G84">
-        <v>-7.288920871675205</v>
+        <v>-5.61053666936052</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.72610978771324</v>
       </c>
       <c r="E85">
-        <v>-22.120239061975</v>
+        <v>-19.90661681212355</v>
       </c>
       <c r="F85">
-        <v>-2.050732997374853</v>
+        <v>-1.245470418174232</v>
       </c>
       <c r="G85">
-        <v>-6.744175749597752</v>
+        <v>-2.806841127126471</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.61139188964514</v>
       </c>
       <c r="E86">
-        <v>-22.40377134806925</v>
+        <v>-21.9692778524553</v>
       </c>
       <c r="F86">
-        <v>-2.194749640555964</v>
+        <v>-0.3887579395857325</v>
       </c>
       <c r="G86">
-        <v>-7.056341325098645</v>
+        <v>-4.90026376327376</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.50346852507265</v>
       </c>
       <c r="E87">
-        <v>-23.21514709297156</v>
+        <v>-20.93135160989725</v>
       </c>
       <c r="F87">
-        <v>-2.186893404107814</v>
+        <v>-0.179237315660848</v>
       </c>
       <c r="G87">
-        <v>-6.048904588480774</v>
+        <v>-2.580266216003695</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.39805365527036</v>
       </c>
       <c r="E88">
-        <v>-24.86629211480428</v>
+        <v>-22.65122528174438</v>
       </c>
       <c r="F88">
-        <v>-2.147106917751354</v>
+        <v>-1.075306357923754</v>
       </c>
       <c r="G88">
-        <v>-6.237971855957538</v>
+        <v>-2.158908149447602</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.29337469957939</v>
       </c>
       <c r="E89">
-        <v>-25.9083936103974</v>
+        <v>-24.27911206107371</v>
       </c>
       <c r="F89">
-        <v>-2.209132583770772</v>
+        <v>-0.9173159850248187</v>
       </c>
       <c r="G89">
-        <v>-6.512311509321151</v>
+        <v>-2.146442788743271</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.19029825241124</v>
       </c>
       <c r="E90">
-        <v>-27.36882194939708</v>
+        <v>-25.05558685679891</v>
       </c>
       <c r="F90">
-        <v>-2.181833736011515</v>
+        <v>-0.2026444933617536</v>
       </c>
       <c r="G90">
-        <v>-6.027025403122397</v>
+        <v>-1.838437802179755</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.08664512016125</v>
       </c>
       <c r="E91">
-        <v>-29.24851905439692</v>
+        <v>-27.73255351016717</v>
       </c>
       <c r="F91">
-        <v>-2.366331865800034</v>
+        <v>-0.01814884867544212</v>
       </c>
       <c r="G91">
-        <v>-5.380030854809528</v>
+        <v>-2.70598293883226</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.983833600593558</v>
       </c>
       <c r="E92">
-        <v>-30.29743137489758</v>
+        <v>-28.89206927983117</v>
       </c>
       <c r="F92">
-        <v>-2.404594984502746</v>
+        <v>-0.6691727309444072</v>
       </c>
       <c r="G92">
-        <v>-5.80234047561786</v>
+        <v>-2.968349414725459</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.885109593478075</v>
       </c>
       <c r="E93">
-        <v>-31.88655668095825</v>
+        <v>-30.59667973003544</v>
       </c>
       <c r="F93">
-        <v>-2.405429150477365</v>
+        <v>-0.07755024676279187</v>
       </c>
       <c r="G93">
-        <v>-5.955832738947125</v>
+        <v>-3.4266540360409</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.784504816502496</v>
       </c>
       <c r="E94">
-        <v>-33.57475820559574</v>
+        <v>-33.13929561654415</v>
       </c>
       <c r="F94">
-        <v>-2.607976577605484</v>
+        <v>-0.3217869201716009</v>
       </c>
       <c r="G94">
-        <v>-5.584418145747339</v>
+        <v>-3.228061382377068</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.684219837058446</v>
       </c>
       <c r="E95">
-        <v>-35.30081550870034</v>
+        <v>-32.19174186552017</v>
       </c>
       <c r="F95">
-        <v>-2.669863077901232</v>
+        <v>-0.4898038521140218</v>
       </c>
       <c r="G95">
-        <v>-6.663060671426719</v>
+        <v>-3.819111103101404</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.583343785382603</v>
       </c>
       <c r="E96">
-        <v>-37.361653838244</v>
+        <v>-34.63376675889648</v>
       </c>
       <c r="F96">
-        <v>-2.919439407588487</v>
+        <v>-0.1940021362483464</v>
       </c>
       <c r="G96">
-        <v>-6.492978551892903</v>
+        <v>-1.607295430646232</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.47845019182259</v>
       </c>
       <c r="E97">
-        <v>-39.37925203372542</v>
+        <v>-38.5483902651681</v>
       </c>
       <c r="F97">
-        <v>-2.804988025380693</v>
+        <v>0.122086297311889</v>
       </c>
       <c r="G97">
-        <v>-6.779281539062252</v>
+        <v>-1.695832631984728</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.3744625720449</v>
       </c>
       <c r="E98">
-        <v>-40.64661567611909</v>
+        <v>-41.8706078587043</v>
       </c>
       <c r="F98">
-        <v>-2.850129906996252</v>
+        <v>0.4704089916172615</v>
       </c>
       <c r="G98">
-        <v>-6.639924778211075</v>
+        <v>-2.593053136420851</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.270911080120284</v>
       </c>
       <c r="E99">
-        <v>-42.65533806254547</v>
+        <v>-41.38610189614963</v>
       </c>
       <c r="F99">
-        <v>-3.001656529051143</v>
+        <v>-0.8959730988916894</v>
       </c>
       <c r="G99">
-        <v>-7.190736878951941</v>
+        <v>-2.748750380638062</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.164277937018811</v>
       </c>
       <c r="E100">
-        <v>-45.23037782294909</v>
+        <v>-46.28462468583079</v>
       </c>
       <c r="F100">
-        <v>-3.089851149692401</v>
+        <v>-0.6033589407919865</v>
       </c>
       <c r="G100">
-        <v>-7.175886070173894</v>
+        <v>-3.134881252531957</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.057109418658888</v>
       </c>
       <c r="E101">
-        <v>-47.03036472846593</v>
+        <v>-47.00245347891965</v>
       </c>
       <c r="F101">
-        <v>-2.908924111777349</v>
+        <v>-0.2528725508305016</v>
       </c>
       <c r="G101">
-        <v>-7.326572889069833</v>
+        <v>-4.223465879536454</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.946055784182629</v>
       </c>
       <c r="E102">
-        <v>-49.46506594725334</v>
+        <v>-47.59685871292945</v>
       </c>
       <c r="F102">
-        <v>-3.31185692711228</v>
+        <v>-1.033555812455256</v>
       </c>
       <c r="G102">
-        <v>-7.563073495409929</v>
+        <v>-2.889327755909352</v>
       </c>
     </row>
   </sheetData>
